--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.42955580630291</v>
+        <v>5.757302818524224</v>
       </c>
       <c r="D2" t="n">
-        <v>35.46116993565698</v>
+        <v>5.762440114544259</v>
       </c>
       <c r="E2" t="n">
-        <v>4.794133291396507</v>
+        <v>0.7790466598519324</v>
       </c>
       <c r="F2" t="n">
-        <v>6.97636811823142</v>
+        <v>1.133659819212606</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.37579189168513</v>
+        <v>3.636066182398834</v>
       </c>
       <c r="D3" t="n">
-        <v>22.36921408978889</v>
+        <v>3.634997289590695</v>
       </c>
       <c r="E3" t="n">
-        <v>4.794133291396507</v>
+        <v>0.7790466598519324</v>
       </c>
       <c r="F3" t="n">
-        <v>6.97636811823142</v>
+        <v>1.133659819212606</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.2574083579234</v>
+        <v>4.266828858162552</v>
       </c>
       <c r="D4" t="n">
-        <v>15.88346779176475</v>
+        <v>2.581063516161772</v>
       </c>
       <c r="E4" t="n">
-        <v>4.794133291396507</v>
+        <v>0.7790466598519324</v>
       </c>
       <c r="F4" t="n">
-        <v>6.97636811823142</v>
+        <v>1.133659819212606</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.22824672285512</v>
+        <v>4.424590092463958</v>
       </c>
       <c r="D5" t="n">
-        <v>26.44902314794088</v>
+        <v>4.297966261540393</v>
       </c>
       <c r="E5" t="n">
-        <v>4.794133291396507</v>
+        <v>0.7790466598519324</v>
       </c>
       <c r="F5" t="n">
-        <v>6.97636811823142</v>
+        <v>1.133659819212606</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.27951221582304</v>
+        <v>3.620420735071244</v>
       </c>
       <c r="D6" t="n">
-        <v>17.81340473868034</v>
+        <v>2.894678270035556</v>
       </c>
       <c r="E6" t="n">
-        <v>4.794133291396507</v>
+        <v>0.7790466598519324</v>
       </c>
       <c r="F6" t="n">
-        <v>6.97636811823142</v>
+        <v>1.133659819212606</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
